--- a/wwwroot/RollNumberList.xlsx
+++ b/wwwroot/RollNumberList.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70d61e5a8e14c1e9/Documents/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{2697F936-1BEC-41AE-94A3-15222D81D8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{736B3B1F-7D0C-4963-A6E7-A1F7BDD68054}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="36" windowWidth="16260" windowHeight="5856"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -774,7 +780,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -827,10 +833,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -843,14 +849,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -888,7 +897,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -960,7 +969,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1133,23 +1142,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:E126"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C2" s="5" t="s">
+    <row r="2" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C2" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="2:5" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="2:5" s="3" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>249</v>
       </c>
@@ -1163,7 +1172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="1">
         <v>2502001</v>
       </c>
@@ -1177,7 +1186,7 @@
         <v>7792010900</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>2502002</v>
       </c>
@@ -1191,7 +1200,7 @@
         <v>9610847252</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="1">
         <v>2502003</v>
       </c>
@@ -1205,7 +1214,7 @@
         <v>7038640332</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>2502004</v>
       </c>
@@ -1219,7 +1228,7 @@
         <v>8602561694</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="1">
         <v>2502005</v>
       </c>
@@ -1233,7 +1242,7 @@
         <v>6376415738</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="1">
         <v>2502006</v>
       </c>
@@ -1247,7 +1256,7 @@
         <v>8766655666</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="1">
         <v>2502007</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>8107774348</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="1">
         <v>2502008</v>
       </c>
@@ -1275,7 +1284,7 @@
         <v>7891450500</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="1">
         <v>2502009</v>
       </c>
@@ -1289,7 +1298,7 @@
         <v>7240154415</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="1">
         <v>2502010</v>
       </c>
@@ -1303,9 +1312,9 @@
         <v>7029685337</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="1">
-        <v>2502011</v>
+        <v>2402126</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -1317,7 +1326,7 @@
         <v>7060841228</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="1">
         <v>2502012</v>
       </c>
@@ -1331,7 +1340,7 @@
         <v>8304912171</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="1">
         <v>2502013</v>
       </c>
@@ -1345,7 +1354,7 @@
         <v>8764612135</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="1">
         <v>2502014</v>
       </c>
@@ -1359,7 +1368,7 @@
         <v>9529647543</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="1">
         <v>2502015</v>
       </c>
@@ -1373,9 +1382,9 @@
         <v>9689210473</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="1">
-        <v>2502016</v>
+        <v>2402091</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -1387,7 +1396,7 @@
         <v>9838862715</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="1">
         <v>2502017</v>
       </c>
@@ -1401,7 +1410,7 @@
         <v>7838688992</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="1">
         <v>2502018</v>
       </c>
@@ -1415,7 +1424,7 @@
         <v>7357714618</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="1">
         <v>2502019</v>
       </c>
@@ -1429,7 +1438,7 @@
         <v>9155142705</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="1">
         <v>2502020</v>
       </c>
@@ -1443,7 +1452,7 @@
         <v>7510963682</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="1">
         <v>2502021</v>
       </c>
@@ -1457,7 +1466,7 @@
         <v>9350062866</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="1">
         <v>2502022</v>
       </c>
@@ -1471,7 +1480,7 @@
         <v>8219772607</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="1">
         <v>2502023</v>
       </c>
@@ -1485,9 +1494,9 @@
         <v>8302112061</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="1">
-        <v>2502024</v>
+        <v>2402110</v>
       </c>
       <c r="C27" t="s">
         <v>49</v>
@@ -1499,7 +1508,7 @@
         <v>9756556388</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="1">
         <v>2502025</v>
       </c>
@@ -1513,7 +1522,7 @@
         <v>9680899892</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="1">
         <v>2502026</v>
       </c>
@@ -1527,7 +1536,7 @@
         <v>9760034664</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="1">
         <v>2502027</v>
       </c>
@@ -1541,7 +1550,7 @@
         <v>6280813310</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="1">
         <v>2502028</v>
       </c>
@@ -1555,7 +1564,7 @@
         <v>9690962383</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="1">
         <v>2502029</v>
       </c>
@@ -1569,7 +1578,7 @@
         <v>8448966485</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="1">
         <v>2502030</v>
       </c>
@@ -1583,7 +1592,7 @@
         <v>9365791029</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="1">
         <v>2502031</v>
       </c>
@@ -1597,7 +1606,7 @@
         <v>9026086775</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="1">
         <v>2502032</v>
       </c>
@@ -1611,7 +1620,7 @@
         <v>6377107164</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="1">
         <v>2502033</v>
       </c>
@@ -1625,7 +1634,7 @@
         <v>8932918502</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="1">
         <v>2502034</v>
       </c>
@@ -1639,7 +1648,7 @@
         <v>7049658593</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B38" s="1">
         <v>2502035</v>
       </c>
@@ -1653,7 +1662,7 @@
         <v>9024292912</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B39" s="1">
         <v>2502036</v>
       </c>
@@ -1667,7 +1676,7 @@
         <v>6350222400</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B40" s="1">
         <v>2502037</v>
       </c>
@@ -1681,7 +1690,7 @@
         <v>9509921949</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="1">
         <v>2502038</v>
       </c>
@@ -1695,7 +1704,7 @@
         <v>9680436111</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B42" s="1">
         <v>2502039</v>
       </c>
@@ -1709,7 +1718,7 @@
         <v>7568076762</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="1">
         <v>2502040</v>
       </c>
@@ -1723,7 +1732,7 @@
         <v>8949659973</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B44" s="1">
         <v>2502041</v>
       </c>
@@ -1737,7 +1746,7 @@
         <v>9746642243</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B45" s="1">
         <v>2502042</v>
       </c>
@@ -1751,7 +1760,7 @@
         <v>9660140960</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B46" s="1">
         <v>2502043</v>
       </c>
@@ -1765,7 +1774,7 @@
         <v>9887696865</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="1">
         <v>2502044</v>
       </c>
@@ -1779,7 +1788,7 @@
         <v>9799001969</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B48" s="1">
         <v>2502045</v>
       </c>
@@ -1793,7 +1802,7 @@
         <v>9896608424</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49" s="1">
         <v>2502046</v>
       </c>
@@ -1807,7 +1816,7 @@
         <v>7878776797</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B50" s="1">
         <v>2502047</v>
       </c>
@@ -1821,7 +1830,7 @@
         <v>8281959319</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B51" s="1">
         <v>2502048</v>
       </c>
@@ -1835,7 +1844,7 @@
         <v>8193805818</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B52" s="1">
         <v>2502049</v>
       </c>
@@ -1849,7 +1858,7 @@
         <v>9462633028</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53" s="1">
         <v>2502050</v>
       </c>
@@ -1863,7 +1872,7 @@
         <v>7665816706</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B54" s="1">
         <v>2502051</v>
       </c>
@@ -1877,7 +1886,7 @@
         <v>8502083542</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" s="1">
         <v>2502052</v>
       </c>
@@ -1891,7 +1900,7 @@
         <v>9713841691</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B56" s="1">
         <v>2502053</v>
       </c>
@@ -1905,7 +1914,7 @@
         <v>7774844049</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B57" s="1">
         <v>2502054</v>
       </c>
@@ -1919,7 +1928,7 @@
         <v>9461537119</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B58" s="1">
         <v>2502055</v>
       </c>
@@ -1933,7 +1942,7 @@
         <v>7851864055</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59" s="1">
         <v>2502056</v>
       </c>
@@ -1947,7 +1956,7 @@
         <v>7030615143</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60" s="1">
         <v>2502057</v>
       </c>
@@ -1961,7 +1970,7 @@
         <v>9024281371</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61" s="1">
         <v>2502058</v>
       </c>
@@ -1975,7 +1984,7 @@
         <v>8962373944</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B62" s="1">
         <v>2502059</v>
       </c>
@@ -1989,7 +1998,7 @@
         <v>8290591310</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B63" s="1">
         <v>2502060</v>
       </c>
@@ -2003,7 +2012,7 @@
         <v>7984557315</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B64" s="1">
         <v>2502061</v>
       </c>
@@ -2017,7 +2026,7 @@
         <v>9664216024</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B65" s="1">
         <v>2502062</v>
       </c>
@@ -2031,7 +2040,7 @@
         <v>7069249139</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B66" s="1">
         <v>2502063</v>
       </c>
@@ -2045,7 +2054,7 @@
         <v>7597799103</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B67" s="1">
         <v>2502064</v>
       </c>
@@ -2059,7 +2068,7 @@
         <v>8350915978</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B68" s="1">
         <v>2502065</v>
       </c>
@@ -2073,7 +2082,7 @@
         <v>8319132272</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B69" s="1">
         <v>2502066</v>
       </c>
@@ -2087,7 +2096,7 @@
         <v>9358752561</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B70" s="1">
         <v>2502067</v>
       </c>
@@ -2101,7 +2110,7 @@
         <v>9462677620</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B71" s="1">
         <v>2502068</v>
       </c>
@@ -2115,7 +2124,7 @@
         <v>7014931420</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B72" s="1">
         <v>2502069</v>
       </c>
@@ -2129,7 +2138,7 @@
         <v>9887044717</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B73" s="1">
         <v>2502070</v>
       </c>
@@ -2143,7 +2152,7 @@
         <v>9079871696</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B74" s="1">
         <v>2502071</v>
       </c>
@@ -2157,7 +2166,7 @@
         <v>9829057383</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B75" s="1">
         <v>2502072</v>
       </c>
@@ -2171,7 +2180,7 @@
         <v>9713240740</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B76" s="1">
         <v>2502073</v>
       </c>
@@ -2185,7 +2194,7 @@
         <v>7427071171</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B77" s="1">
         <v>2502074</v>
       </c>
@@ -2199,7 +2208,7 @@
         <v>8288979021</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B78" s="1">
         <v>2502075</v>
       </c>
@@ -2213,7 +2222,7 @@
         <v>6378674795</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B79" s="1">
         <v>2502076</v>
       </c>
@@ -2227,7 +2236,7 @@
         <v>8239270800</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B80" s="1">
         <v>2502077</v>
       </c>
@@ -2241,7 +2250,7 @@
         <v>8000772723</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B81" s="1">
         <v>2502078</v>
       </c>
@@ -2255,7 +2264,7 @@
         <v>9479638514</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B82" s="1">
         <v>2502079</v>
       </c>
@@ -2269,7 +2278,7 @@
         <v>9079871696</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B83" s="1">
         <v>2502080</v>
       </c>
@@ -2283,7 +2292,7 @@
         <v>9799942470</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B84" s="1">
         <v>2502081</v>
       </c>
@@ -2297,7 +2306,7 @@
         <v>6378246143</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B85" s="1">
         <v>2502082</v>
       </c>
@@ -2311,7 +2320,7 @@
         <v>7014505687</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B86" s="1">
         <v>2502083</v>
       </c>
@@ -2325,7 +2334,7 @@
         <v>9636954220</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B87" s="1">
         <v>2502084</v>
       </c>
@@ -2339,7 +2348,7 @@
         <v>8107573089</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B88" s="1">
         <v>2502085</v>
       </c>
@@ -2353,7 +2362,7 @@
         <v>8290393788</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B89" s="1">
         <v>2502086</v>
       </c>
@@ -2367,7 +2376,7 @@
         <v>7355810879</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B90" s="1">
         <v>2502087</v>
       </c>
@@ -2381,7 +2390,7 @@
         <v>7060937288</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B91" s="1">
         <v>2502088</v>
       </c>
@@ -2395,7 +2404,7 @@
         <v>9518140687</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B92" s="1">
         <v>2502089</v>
       </c>
@@ -2409,7 +2418,7 @@
         <v>8000858489</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B93" s="1">
         <v>2502090</v>
       </c>
@@ -2423,7 +2432,7 @@
         <v>9509206298</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B94" s="1">
         <v>2502091</v>
       </c>
@@ -2437,7 +2446,7 @@
         <v>8955175022</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B95" s="1">
         <v>2502092</v>
       </c>
@@ -2451,7 +2460,7 @@
         <v>8302781414</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B96" s="1">
         <v>2502093</v>
       </c>
@@ -2465,7 +2474,7 @@
         <v>6367314276</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="1">
         <v>2502094</v>
       </c>
@@ -2479,7 +2488,7 @@
         <v>9462127502</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="1">
         <v>2502095</v>
       </c>
@@ -2493,7 +2502,7 @@
         <v>7878067223</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="1">
         <v>2502096</v>
       </c>
@@ -2507,7 +2516,7 @@
         <v>8000829388</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="1">
         <v>2502097</v>
       </c>
@@ -2521,7 +2530,7 @@
         <v>9691185359</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="1">
         <v>2502098</v>
       </c>
@@ -2535,7 +2544,7 @@
         <v>9588089398</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="1">
         <v>2502099</v>
       </c>
@@ -2549,7 +2558,7 @@
         <v>9602218321</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="1">
         <v>2502100</v>
       </c>
@@ -2563,7 +2572,7 @@
         <v>7891242556</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" s="1">
         <v>2502101</v>
       </c>
@@ -2577,7 +2586,7 @@
         <v>9587449434</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B105" s="1">
         <v>2502102</v>
       </c>
@@ -2591,7 +2600,7 @@
         <v>7050994815</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B106" s="1">
         <v>2502103</v>
       </c>
@@ -2605,7 +2614,7 @@
         <v>8302068947</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B107" s="1">
         <v>2502104</v>
       </c>
@@ -2619,7 +2628,7 @@
         <v>8104019992</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B108" s="1">
         <v>2502105</v>
       </c>
@@ -2633,7 +2642,7 @@
         <v>8107411709</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B109" s="1">
         <v>2502106</v>
       </c>
@@ -2647,7 +2656,7 @@
         <v>7084887106</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B110" s="1">
         <v>2502107</v>
       </c>
@@ -2661,7 +2670,7 @@
         <v>6263311850</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B111" s="1">
         <v>2502108</v>
       </c>
@@ -2675,7 +2684,7 @@
         <v>9632005663</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B112" s="1">
         <v>2502109</v>
       </c>
@@ -2689,7 +2698,7 @@
         <v>8058726425</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B113" s="1">
         <v>2502110</v>
       </c>
@@ -2703,7 +2712,7 @@
         <v>7665379038</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B114" s="1">
         <v>2502111</v>
       </c>
@@ -2717,7 +2726,7 @@
         <v>9460706485</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B115" s="1">
         <v>2502112</v>
       </c>
@@ -2731,7 +2740,7 @@
         <v>9887622828</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B116" s="1">
         <v>2502113</v>
       </c>
@@ -2745,7 +2754,7 @@
         <v>8780201891</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B117" s="1">
         <v>2502114</v>
       </c>
@@ -2759,7 +2768,7 @@
         <v>9351105789</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B118" s="1">
         <v>2502115</v>
       </c>
@@ -2773,7 +2782,7 @@
         <v>7891958364</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B119" s="1">
         <v>2502116</v>
       </c>
@@ -2787,7 +2796,7 @@
         <v>7690040266</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B120" s="1">
         <v>2502117</v>
       </c>
@@ -2801,7 +2810,7 @@
         <v>8989161004</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B121" s="1">
         <v>2502118</v>
       </c>
@@ -2815,7 +2824,7 @@
         <v>6377548160</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B122" s="1">
         <v>2502119</v>
       </c>
@@ -2829,7 +2838,7 @@
         <v>9799693009</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B123" s="1">
         <v>2502120</v>
       </c>
@@ -2843,7 +2852,7 @@
         <v>8302110846</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B124" s="1">
         <v>2502121</v>
       </c>
@@ -2857,7 +2866,7 @@
         <v>8949463655</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B125" s="1">
         <v>2502122</v>
       </c>
@@ -2871,7 +2880,7 @@
         <v>9691314733</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B126" s="1">
         <v>2502123</v>
       </c>
@@ -2895,18 +2904,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
